--- a/213332_XPath_CSS_Selector_Cheat_sheet.xlsx
+++ b/213332_XPath_CSS_Selector_Cheat_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infics-my.sharepoint.com/personal/nares_infinite_com/Documents/Documents/ATB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D862D10-13A4-4341-B2F2-B26B8FB38E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{3D862D10-13A4-4341-B2F2-B26B8FB38E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4125CDCE-082B-4297-8336-2857543C8560}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="767" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="767" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XPath&amp;CSS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Operators" sheetId="6" r:id="rId6"/>
     <sheet name="Obj class obj" sheetId="7" r:id="rId7"/>
     <sheet name="Response Codes" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="620">
   <si>
     <t>Xpath</t>
   </si>
@@ -219,29 +218,6 @@
   </si>
   <si>
     <t>CSS Selectors Practice - H Y R Tutorials</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Note:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="20"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> You can test any of the above mentioned xpath or css selector in the specified webpage for real-time confirmation</t>
-    </r>
   </si>
   <si>
     <t>Action / Purpose</t>
@@ -2851,6 +2827,873 @@
   </si>
   <si>
     <t>Move the build to production (Go-Live) 🚀</t>
+  </si>
+  <si>
+    <t>Attribute / Function</t>
+  </si>
+  <si>
+    <t>Examples</t>
+  </si>
+  <si>
+    <t>@id</t>
+  </si>
+  <si>
+    <t>@type</t>
+  </si>
+  <si>
+    <t>❌ Rarely, only if type is dynamic</t>
+  </si>
+  <si>
+    <t>//input[@type='text']</t>
+  </si>
+  <si>
+    <t>@value</t>
+  </si>
+  <si>
+    <t>text()</t>
+  </si>
+  <si>
+    <t>@class</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> You can test any of the above mentioned xpath or css selector in the specified webpage for real-time confirmation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When to use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When to use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if the ID is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fixed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and exact</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if the ID is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dynamic or partially known</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//input[@id='username']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//input[contains(@id,'user')]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> almost always (e.g., text, button, checkbox)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for exact match</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if value is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>partial or dynamic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//button[@value='Login']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//button[contains(@value,'Log')]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exact visible text</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>partial text</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//h4[text()='Fish']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//h4[contains(text(),'Fish')]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ Avoid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (because elements often have </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiple classes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (check for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>one class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at a time)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//div[contains(@class,'Invertebrate')]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//a[contains(@class,'js-selected-navigation-item')]</t>
+    </r>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Why </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Wrong Example</t>
+  </si>
+  <si>
+    <t>Proper Example</t>
+  </si>
+  <si>
+    <r>
+      <t>Attribute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (id, class, type, value, name)</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ Yes</t>
+  </si>
+  <si>
+    <r>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the attribute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the element</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//input[id='username']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ❌ (missing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//input[@id='username']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ✅</t>
+    </r>
+  </si>
+  <si>
+    <t>Text inside an element</t>
+  </si>
+  <si>
+    <t>❌ No</t>
+  </si>
+  <si>
+    <r>
+      <t>text()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not an attribute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, it’s the content of the element</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//h4[@text='Fish']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ❌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//h4[text()='Fish']</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ✅</t>
+    </r>
+  </si>
+  <si>
+    <t>Element itself</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Element names are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>direct nodes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, not attributes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//@div</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ❌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//div</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ✅</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Functions like </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains()</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ If checking an attribute ❌ If checking text</t>
+  </si>
+  <si>
+    <r>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> required when checking </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>attribute value</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>contains(@text,'Fish')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ❌ (text() is not an attribute)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>contains(@class,'menu')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>contains(text(),'Fish')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ✅</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2866,60 +3709,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2972,6 +3764,54 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
@@ -3072,117 +3912,152 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3197,11 +4072,42 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="24"/>
+        <sz val="9"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3214,12 +4120,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3229,12 +4129,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="24"/>
+        <sz val="9"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3245,12 +4145,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3260,12 +4154,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="24"/>
+        <sz val="9"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -3278,12 +4172,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3294,12 +4182,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="24"/>
+        <sz val="9"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -3310,49 +4198,13 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="24"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -3369,7 +4221,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:D21" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:D21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="6">
   <autoFilter ref="A2:D21" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3377,10 +4229,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Xpath" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CSS Selector" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{D72E3976-2F04-499A-B245-2902252C49BB}" name="Webpage" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Xpath" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CSS Selector" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{D72E3976-2F04-499A-B245-2902252C49BB}" name="Webpage" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3649,318 +4501,496 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="41" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="96.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="93.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" style="41" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36.6">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" ht="31.2">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="31.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="31.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="31.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="31.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="31.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="31.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="31.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="31.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="31.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="31.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="31.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="31.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="31.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="31.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="31.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="31.2">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="31.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="31.2">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="36.6">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:4" ht="25.8">
-      <c r="A23" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="40" t="s">
+        <v>580</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="45" t="s">
+        <v>571</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>581</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="24">
+      <c r="A29" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>575</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="24">
+      <c r="A31" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>588</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="36">
+      <c r="A33" s="43" t="s">
+        <v>579</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>593</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+    </row>
+    <row r="37" spans="1:5" s="49" customFormat="1" ht="15">
+      <c r="A37" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>597</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="D37" s="48" t="s">
+        <v>599</v>
+      </c>
+      <c r="E37" s="48" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30">
+      <c r="A38" s="28" t="s">
+        <v>601</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30">
+      <c r="A39" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>607</v>
+      </c>
+      <c r="C39" s="29" t="s">
+        <v>608</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15">
+      <c r="A40" s="28" t="s">
+        <v>611</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>607</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>612</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>613</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="45">
+      <c r="A41" s="28" t="s">
+        <v>615</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>616</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>619</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3996,388 +5026,388 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6BE014-8364-4234-ADDD-EF06B3FE17B4}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="49.77734375" customWidth="1"/>
-    <col min="3" max="3" width="39.88671875" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="13" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="14" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A3" s="16" t="s">
+      <c r="B3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="17" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A4" s="5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="17" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A5" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A5" s="16" t="s">
+      <c r="B5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="17" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A6" s="16" t="s">
+      <c r="B6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="C6" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="17" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A7" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A7" s="16" t="s">
+      <c r="B7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A8" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A9" s="16" t="s">
+      <c r="B9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="17" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A10" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A10" s="16" t="s">
+      <c r="B10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="16" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A11" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A11" s="16" t="s">
+      <c r="B11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="16" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1">
-      <c r="A12" s="12"/>
-    </row>
-    <row r="13" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A13" s="13" t="s">
+      <c r="B13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="13" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A14" s="7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A14" s="18" t="s">
+      <c r="B14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="C14" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A15" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A15" s="18" t="s">
+      <c r="B15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="17" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A16" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A16" s="18" t="s">
+      <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A17" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A17" s="18" t="s">
+      <c r="B17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A18" s="18" t="s">
+      <c r="B18" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="17" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A19" s="7" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A19" s="18" t="s">
+      <c r="B19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="17" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A20" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A20" s="18" t="s">
+      <c r="B20" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="17" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A21" s="7" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A21" s="18" t="s">
+      <c r="B21" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="17" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A22" s="7" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A22" s="18" t="s">
+      <c r="B22" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="17" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A23" s="18" t="s">
+      <c r="B23" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="17" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A24" s="7" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A24" s="18" t="s">
+      <c r="B24" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A25" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A25" s="18" t="s">
+      <c r="B25" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="C25" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="17" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A26" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A26" s="18" t="s">
+      <c r="B26" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A27" s="18" t="s">
+      <c r="B27" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="C27" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A28" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A28" s="18" t="s">
+      <c r="B28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="17" t="s">
+    </row>
+    <row r="29" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A29" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A29" s="18" t="s">
+      <c r="B29" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="C29" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="17" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A30" s="7" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A30" s="18" t="s">
+      <c r="B30" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="C30" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="17" t="s">
+    </row>
+    <row r="31" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A31" s="7" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A31" s="18" t="s">
+      <c r="B31" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="C31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C31" s="16" t="s">
+    </row>
+    <row r="32" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A32" s="7" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A32" s="18" t="s">
+      <c r="B32" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="C32" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="17" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A33" s="7" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A33" s="18" t="s">
+      <c r="B33" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="C33" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C33" s="17" t="s">
+    </row>
+    <row r="34" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A34" s="7" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A34" s="18" t="s">
+      <c r="B34" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="C34" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16.5" thickBot="1">
+      <c r="A35" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="16.2" thickBot="1">
-      <c r="A35" s="18" t="s">
+      <c r="B35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="12"/>
+      <c r="A36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4388,273 +5418,273 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614ECD69-356F-43A5-8E86-B9B5DC3D0402}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
+      <c r="B3" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="C3" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="25" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
+      <c r="B4" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="C4" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="25" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
+      <c r="B5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="C5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="25" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="13" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
+      <c r="B6" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="25" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="24" t="s">
+      <c r="B7" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="C7" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="25" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="24" t="s">
+      <c r="B8" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="25" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="13" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="24" t="s">
+      <c r="B9" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="C9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="25" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="13" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="24" t="s">
+      <c r="B10" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="25" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="13" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="24" t="s">
+      <c r="B11" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="30" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="23" t="s">
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="B18" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="24" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="B19" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="G19" s="31"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C20" s="24" t="s">
+    <row r="21" spans="1:7">
+      <c r="A21" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="B21" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="24" t="s">
+    <row r="22" spans="1:7">
+      <c r="A22" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="B22" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="C22" s="24" t="s">
+    <row r="23" spans="1:7">
+      <c r="A23" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="B23" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G23" s="17" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="C23" s="24" t="s">
+    <row r="24" spans="1:7">
+      <c r="A24" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="G23" s="33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="24" t="s">
+      <c r="B24" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="C24" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="C24" s="24" t="s">
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="13" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="24" t="s">
+      <c r="B25" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="C25" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="24" t="s">
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="13" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="24" t="s">
+      <c r="B26" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="C26" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="C26" s="24" t="s">
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="13" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="24" t="s">
+      <c r="B27" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="C27" s="13" t="s">
         <v>209</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4670,393 +5700,393 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBCD4C73-4A67-43A5-895B-5D5BA0029292}">
   <dimension ref="A2:S21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="16" max="16" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="13.88671875" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="P2" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="P2" s="20" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="R2" s="23" t="s">
-        <v>536</v>
-      </c>
-      <c r="S2" s="23" t="s">
+      <c r="C3" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="L3" t="s">
+        <v>524</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="34" t="s">
+      <c r="Q3" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="S3" s="14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="L3" t="s">
+      <c r="B4" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="L4" t="s">
         <v>525</v>
       </c>
-      <c r="P3" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>539</v>
-      </c>
-      <c r="R3" s="25" t="s">
-        <v>540</v>
-      </c>
-      <c r="S3" s="25" t="s">
+      <c r="P4" s="1" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="35">
+      <c r="Q4" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="19">
         <v>0</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="E5" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="L5" t="s">
         <v>526</v>
       </c>
-      <c r="P4" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="Q4" s="23" t="s">
-        <v>543</v>
-      </c>
-      <c r="R4" s="25" t="s">
-        <v>544</v>
-      </c>
-      <c r="S4" s="25" t="s">
+      <c r="P5" s="1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="35" t="s">
+      <c r="Q5" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="L6" t="s">
+        <v>527</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="L7" t="s">
+        <v>528</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="L8" t="s">
+        <v>529</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="L9" t="s">
+        <v>530</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="C10" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="35">
+      <c r="D10" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="L10" t="s">
+        <v>531</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="L5" t="s">
-        <v>527</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>547</v>
-      </c>
-      <c r="R5" s="25" t="s">
-        <v>548</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="D6" s="35">
+      <c r="E11" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="L11" t="s">
+        <v>532</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="R11" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="S11" s="14" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="H13" s="17" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="G14" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="H14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="13">
         <v>0</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="L6" t="s">
-        <v>528</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>551</v>
-      </c>
-      <c r="R6" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="S6" s="25" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="L7" t="s">
-        <v>529</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>555</v>
-      </c>
-      <c r="R7" s="25" t="s">
-        <v>556</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="L8" t="s">
-        <v>530</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q8" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="R8" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="L9" t="s">
-        <v>531</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q9" s="23" t="s">
-        <v>562</v>
-      </c>
-      <c r="R9" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="S9" s="25" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="L10" t="s">
-        <v>532</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q10" s="23" t="s">
-        <v>565</v>
-      </c>
-      <c r="R10" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="S10" s="25" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="35" t="b">
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="13">
         <v>0</v>
       </c>
-      <c r="E11" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="L11" t="s">
-        <v>533</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>568</v>
-      </c>
-      <c r="Q11" s="23" t="s">
-        <v>569</v>
-      </c>
-      <c r="R11" s="25" t="s">
-        <v>570</v>
-      </c>
-      <c r="S11" s="25" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="H13" s="33" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14" s="27"/>
-      <c r="G14" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="13" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="B19" s="24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="24" t="s">
+      <c r="B21" s="13" t="s">
         <v>260</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5071,588 +6101,588 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE2FE79B-BB56-476F-91F5-D168D765D13A}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
-    <col min="12" max="12" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="12" max="12" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="J1" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="J1" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="M2" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="M2" s="23" t="s">
+      <c r="D3" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="24" t="s">
+      <c r="M3" s="13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="J3" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="M3" s="24" t="s">
+      <c r="D4" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L4" s="13" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" s="24" t="s">
+      <c r="M4" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="M4" s="24" t="s">
+      <c r="D5" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="M5" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="J5" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="M5" s="24" t="s">
+      <c r="D6" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="M6" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="J6" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="M6" s="24" t="s">
+      <c r="D7" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="D7" s="24" t="s">
+      <c r="M7" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="M7" s="24" t="s">
+      <c r="D8" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="M8" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="J8" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="M8" s="24" t="s">
+      <c r="D9" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="24" t="s">
+      <c r="M9" s="13" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="J9" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="M9" s="24" t="s">
+      <c r="D10" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="D10" s="24" t="s">
+      <c r="M10" s="13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="J10" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="M10" s="24" t="s">
+      <c r="D11" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L11" s="13" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="D11" s="24" t="s">
+      <c r="M11" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="J11" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="M11" s="24" t="s">
+      <c r="D12" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L12" s="13" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="M12" s="13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="J12" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="K12" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="M12" s="24" t="s">
+      <c r="D13" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="D13" s="24" t="s">
+      <c r="M13" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="M13" s="24" t="s">
+      <c r="D14" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="D14" s="24" t="s">
+      <c r="M14" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="M14" s="24" t="s">
+      <c r="D15" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L15" s="13" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="D15" s="24" t="s">
+      <c r="M15" s="13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="M15" s="24" t="s">
+      <c r="D16" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L16" s="13" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="M16" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L16" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="M16" s="24" t="s">
+      <c r="D17" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="L17" s="13" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" s="24" t="s">
+      <c r="M17" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="J17" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L17" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="M17" s="24" t="s">
+      <c r="D18" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="L18" s="13" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="D18" s="24" t="s">
+      <c r="M18" s="13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="J18" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="M18" s="24" t="s">
+      <c r="D19" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="D19" s="24" t="s">
+      <c r="M19" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="J19" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L19" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="M19" s="24" t="s">
+      <c r="D20" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L20" s="13" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L20" s="24" t="s">
+      <c r="M20" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="M20" s="24" t="s">
+    </row>
+    <row r="21" spans="1:13">
+      <c r="J21" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="J21" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L21" s="24" t="s">
+      <c r="M21" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="M21" s="24" t="s">
+    </row>
+    <row r="22" spans="1:13">
+      <c r="J22" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="L22" s="13" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="J22" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L22" s="24" t="s">
+      <c r="M22" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="M22" s="24" t="s">
+    </row>
+    <row r="23" spans="1:13">
+      <c r="J23" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="J23" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="L23" s="24" t="s">
+      <c r="M23" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="M23" s="24" t="s">
+    </row>
+    <row r="24" spans="1:13">
+      <c r="J24" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="L24" s="13" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="J24" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K24" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L24" s="24" t="s">
+      <c r="M24" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="M24" s="24" t="s">
+    </row>
+    <row r="25" spans="1:13">
+      <c r="J25" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="L25" s="13" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="J25" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="K25" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="L25" s="24" t="s">
+      <c r="M25" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5667,143 +6697,143 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027126ED-EDB5-4B86-9811-5D91835B0559}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="22" t="s">
+      <c r="B3" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="C3" s="1">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C3" s="12">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="10">
         <v>7</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="C4" s="12">
-        <v>6</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="C5" s="12">
-        <v>3</v>
-      </c>
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="22" t="s">
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B7" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="C6" s="21">
-        <v>7</v>
-      </c>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="22" t="s">
-        <v>365</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>377</v>
-      </c>
-      <c r="C7" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="22" t="s">
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="22" t="s">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="C10" s="12">
-        <v>5</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>369</v>
-      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="19"/>
-      <c r="C11" s="22">
+      <c r="B11" s="8"/>
+      <c r="C11" s="11">
         <v>42</v>
       </c>
     </row>
@@ -5818,132 +6848,132 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6B9D69-27EF-4ACD-B547-C3D443618A5D}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.21875" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="41.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="A1" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="10" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="21" t="s">
+      <c r="B3" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="D3" s="21" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="10" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="21" t="s">
+      <c r="B4" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="D4" s="21" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="10" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="21" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="21" t="s">
+      <c r="B6" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="D6" s="21" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="10" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="21" t="s">
+      <c r="B7" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="D7" s="21" t="s">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="21" t="s">
+      <c r="B8" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D8" s="12" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="10" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="21" t="s">
+      <c r="B9" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="C9" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -5957,729 +6987,729 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E9FD33-2EEE-4C4C-87A3-193EF64E23F7}">
   <dimension ref="A1:Y31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="H1" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>514</v>
+      </c>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="U1" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="H2" s="11">
+        <v>100</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="H1" s="20" t="s">
+      <c r="O2" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H3" s="11">
+        <v>101</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="O3" s="11">
+        <v>400</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="U3" s="11">
+        <v>500</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H4" s="11">
+        <v>102</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="O4" s="11">
+        <v>401</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="U4" s="11">
+        <v>501</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H5" s="11">
+        <v>103</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="O5" s="11">
+        <v>402</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="U5" s="11">
+        <v>502</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O6" s="11">
+        <v>403</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="U6" s="11">
+        <v>503</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="O7" s="11">
+        <v>404</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="U7" s="11">
+        <v>504</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="H8" s="11">
+        <v>200</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O8" s="11">
+        <v>405</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="U8" s="11">
+        <v>505</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="H9" s="11">
+        <v>201</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="O9" s="11">
+        <v>406</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="U9" s="11">
+        <v>506</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="H10" s="11">
+        <v>202</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="O10" s="11">
+        <v>407</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="U10" s="11">
+        <v>507</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="12">
+        <v>200</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="C11" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="H11" s="11">
+        <v>203</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="O11" s="11">
+        <v>408</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="U11" s="11">
+        <v>508</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="12">
+        <v>201</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="H12" s="11">
+        <v>204</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="O12" s="11">
+        <v>409</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="U12" s="11">
+        <v>510</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="12">
+        <v>202</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="H13" s="11">
+        <v>205</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="O13" s="11">
+        <v>410</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="U13" s="11">
+        <v>511</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="12">
+        <v>204</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="H14" s="11">
+        <v>206</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="O14" s="11">
+        <v>411</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="12">
+        <v>301</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="H15" s="11">
+        <v>207</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="O15" s="11">
         <v>412</v>
       </c>
-      <c r="N1" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="U1" s="38" t="s">
-        <v>524</v>
-      </c>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-    </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="P15" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="12">
+        <v>302</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="H16" s="11">
+        <v>208</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="O16" s="11">
+        <v>413</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="12">
+        <v>400</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="H17" s="11">
+        <v>226</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="O17" s="11">
+        <v>414</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="14.45" customHeight="1">
+      <c r="A18" s="12">
+        <v>401</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="11">
+        <v>415</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="12">
+        <v>403</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="H2" s="22">
-        <v>100</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="O2" s="20" t="s">
+      <c r="O19" s="11">
+        <v>416</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="12">
+        <v>404</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="H20" s="11">
+        <v>300</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="O20" s="11">
+        <v>417</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="12">
+        <v>405</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="H21" s="11">
+        <v>301</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="O21" s="11">
+        <v>418</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="12">
+        <v>409</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="H22" s="11">
+        <v>302</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="O22" s="11">
+        <v>421</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="12">
+        <v>415</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="H23" s="11">
+        <v>303</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="O23" s="11">
+        <v>422</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="12">
+        <v>429</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="H24" s="11">
+        <v>304</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="O24" s="11">
+        <v>423</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="12">
+        <v>500</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="H25" s="11">
+        <v>305</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="O25" s="11">
+        <v>424</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="12">
+        <v>502</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="H26" s="11">
+        <v>307</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="O26" s="11">
+        <v>425</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="12">
+        <v>503</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="H27" s="11">
+        <v>308</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="O27" s="11">
+        <v>426</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="O28" s="11">
         <v>428</v>
       </c>
-      <c r="P2" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="H3" s="22">
-        <v>101</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="O3" s="22">
-        <v>400</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="U3" s="22">
-        <v>500</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="H4" s="22">
-        <v>102</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="O4" s="22">
-        <v>401</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="U4" s="22">
-        <v>501</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="22" t="s">
-        <v>419</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="H5" s="22">
-        <v>103</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="O5" s="22">
-        <v>402</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="U5" s="22">
-        <v>502</v>
-      </c>
-      <c r="V5" s="12" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="22" t="s">
-        <v>422</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="O6" s="22">
-        <v>403</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="U6" s="22">
-        <v>503</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="O7" s="22">
-        <v>404</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="U7" s="22">
-        <v>504</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="H8" s="22">
-        <v>200</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="O8" s="22">
-        <v>405</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="U8" s="22">
-        <v>505</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="28" t="s">
-        <v>463</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="H9" s="22">
-        <v>201</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="O9" s="22">
-        <v>406</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="U9" s="22">
-        <v>506</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="H10" s="22">
-        <v>202</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="O10" s="22">
-        <v>407</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="U10" s="22">
-        <v>507</v>
-      </c>
-      <c r="V10" s="12" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" s="23">
-        <v>200</v>
-      </c>
-      <c r="B11" s="25" t="s">
+      <c r="P28" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="O29" s="11">
         <v>429</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="H11" s="22">
-        <v>203</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="O11" s="22">
-        <v>408</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="U11" s="22">
-        <v>508</v>
-      </c>
-      <c r="V11" s="12" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" s="23">
-        <v>201</v>
-      </c>
-      <c r="B12" s="25" t="s">
+      <c r="P29" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="O30" s="11">
         <v>431</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="H12" s="22">
-        <v>204</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="O12" s="22">
-        <v>409</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="U12" s="22">
-        <v>510</v>
-      </c>
-      <c r="V12" s="12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" s="23">
-        <v>202</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>433</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="H13" s="22">
-        <v>205</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="O13" s="22">
-        <v>410</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="U13" s="22">
-        <v>511</v>
-      </c>
-      <c r="V13" s="12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="23">
-        <v>204</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>435</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="H14" s="22">
-        <v>206</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="O14" s="22">
-        <v>411</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" s="23">
-        <v>301</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="H15" s="22">
-        <v>207</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="O15" s="22">
-        <v>412</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" s="23">
-        <v>302</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>440</v>
-      </c>
-      <c r="H16" s="22">
-        <v>208</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="O16" s="22">
-        <v>413</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="23">
-        <v>400</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>441</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="H17" s="22">
-        <v>226</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="O17" s="22">
-        <v>414</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="14.4" customHeight="1">
-      <c r="A18" s="23">
-        <v>401</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>479</v>
-      </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="22">
-        <v>415</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="23">
-        <v>403</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>446</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="O19" s="22">
-        <v>416</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="23">
-        <v>404</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="H20" s="22">
-        <v>300</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="O20" s="22">
-        <v>417</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="23">
-        <v>405</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>450</v>
-      </c>
-      <c r="H21" s="22">
-        <v>301</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="O21" s="22">
-        <v>418</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="23">
-        <v>409</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="P30" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="O31" s="11">
         <v>451</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="H22" s="22">
-        <v>302</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="O22" s="22">
-        <v>421</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="23">
-        <v>415</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>453</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>454</v>
-      </c>
-      <c r="H23" s="22">
-        <v>303</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="O23" s="22">
-        <v>422</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="23">
-        <v>429</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>456</v>
-      </c>
-      <c r="H24" s="22">
-        <v>304</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="O24" s="22">
-        <v>423</v>
-      </c>
-      <c r="P24" s="12" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="23">
-        <v>500</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>457</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="H25" s="22">
-        <v>305</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="O25" s="22">
-        <v>424</v>
-      </c>
-      <c r="P25" s="12" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="23">
-        <v>502</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>460</v>
-      </c>
-      <c r="H26" s="22">
-        <v>307</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="O26" s="22">
-        <v>425</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="23">
-        <v>503</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>462</v>
-      </c>
-      <c r="H27" s="22">
-        <v>308</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="O27" s="22">
-        <v>426</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="O28" s="22">
-        <v>428</v>
-      </c>
-      <c r="P28" s="12" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="O29" s="22">
-        <v>429</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="O30" s="22">
-        <v>431</v>
-      </c>
-      <c r="P30" s="12" t="s">
+      <c r="P31" s="1" t="s">
         <v>513</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="O31" s="22">
-        <v>451</v>
-      </c>
-      <c r="P31" s="12" t="s">
-        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -6693,13 +7723,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B25459F-A33A-44A1-BA14-27B66D1C0E8C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/213332_XPath_CSS_Selector_Cheat_sheet.xlsx
+++ b/213332_XPath_CSS_Selector_Cheat_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infics-my.sharepoint.com/personal/nares_infinite_com/Documents/Documents/ATB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{3D862D10-13A4-4341-B2F2-B26B8FB38E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4125CDCE-082B-4297-8336-2857543C8560}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{3D862D10-13A4-4341-B2F2-B26B8FB38E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9966E0-CD09-4D12-9445-F50CAF747EC2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="767" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="687">
   <si>
     <t>Xpath</t>
   </si>
@@ -3694,13 +3694,576 @@
       </rPr>
       <t xml:space="preserve"> ✅</t>
     </r>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of an element</t>
+    </r>
+  </si>
+  <si>
+    <t>//h4[text()='Fish']</t>
+  </si>
+  <si>
+    <t>contains()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Checks if an attribute or text </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contains a value</t>
+    </r>
+  </si>
+  <si>
+    <t>//div[contains(@class,'menu')]</t>
+  </si>
+  <si>
+    <t>starts-with()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Checks if an attribute or text </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>starts with a value</t>
+    </r>
+  </si>
+  <si>
+    <t>//a[starts-with(@href,'http')]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Checks if a string </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ends with</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a value</t>
+    </r>
+  </si>
+  <si>
+    <t>//img[ends-with(@src,'.png')]</t>
+  </si>
+  <si>
+    <t>not()</t>
+  </si>
+  <si>
+    <t>Negates a condition</t>
+  </si>
+  <si>
+    <t>//input[not(@disabled)]</t>
+  </si>
+  <si>
+    <t>position()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>position of the node</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the current selection</t>
+    </r>
+  </si>
+  <si>
+    <t>//li[position()=1]</t>
+  </si>
+  <si>
+    <t>last()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>position of the last node</t>
+    </r>
+  </si>
+  <si>
+    <t>//li[position()=last()]</t>
+  </si>
+  <si>
+    <t>normalize-space()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Removes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>leading/trailing spaces</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from text</t>
+    </r>
+  </si>
+  <si>
+    <t>//span[normalize-space(text())='Hello']</t>
+  </si>
+  <si>
+    <t>count()</t>
+  </si>
+  <si>
+    <t>Counts number of nodes in a node-set</t>
+  </si>
+  <si>
+    <t>count(//li)</t>
+  </si>
+  <si>
+    <t>string-length()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>length of string</t>
+    </r>
+  </si>
+  <si>
+    <t>string-length(//span/text())</t>
+  </si>
+  <si>
+    <t>XPath Functions</t>
+  </si>
+  <si>
+    <r>
+      <t>ends-with()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(XPath 2.0)</t>
+    </r>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>direct children</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the current node</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>//div/child::p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>//div/p</t>
+    </r>
+  </si>
+  <si>
+    <t>descendant</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all descendants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (children, grandchildren…)</t>
+    </r>
+  </si>
+  <si>
+    <t>//div/descendant::span</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parent node</t>
+    </r>
+  </si>
+  <si>
+    <t>//span/parent::div</t>
+  </si>
+  <si>
+    <t>ancestor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all ancestors</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (parent, grandparent…)</t>
+    </r>
+  </si>
+  <si>
+    <t>//span/ancestor::div</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>siblings after the current node</t>
+    </r>
+  </si>
+  <si>
+    <t>//div/following-sibling::p</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>siblings before the current node</t>
+    </r>
+  </si>
+  <si>
+    <t>//p/preceding-sibling::div</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">All nodes in the document </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>after the current node</t>
+    </r>
+  </si>
+  <si>
+    <t>//div/following::span</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">All nodes in the document </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>before the current node</t>
+    </r>
+  </si>
+  <si>
+    <t>//span/preceding::div</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>current node</t>
+    </r>
+  </si>
+  <si>
+    <t>//div/self::div</t>
+  </si>
+  <si>
+    <t>descendant-or-self</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>current node + all descendants</t>
+    </r>
+  </si>
+  <si>
+    <t>//div/descendant-or-self::span</t>
+  </si>
+  <si>
+    <t>ancestor-or-self</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Selects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>current node + all ancestors</t>
+    </r>
+  </si>
+  <si>
+    <t>//span/ancestor-or-self::div</t>
+  </si>
+  <si>
+    <t>Xpath Axes</t>
+  </si>
+  <si>
+    <t>following(down)</t>
+  </si>
+  <si>
+    <t>preceding(up)</t>
+  </si>
+  <si>
+    <t>preceding-sibling(up)</t>
+  </si>
+  <si>
+    <t>following-sibling(down)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3815,6 +4378,24 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3914,7 +4495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3972,24 +4553,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3998,12 +4561,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4018,15 +4575,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -4052,12 +4600,53 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4065,37 +4654,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4201,10 +4759,41 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -4220,8 +4809,12 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:D21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:D21" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5">
   <autoFilter ref="A2:D21" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4229,10 +4822,10 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Xpath" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CSS Selector" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{D72E3976-2F04-499A-B245-2902252C49BB}" name="Webpage" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Description" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Xpath" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CSS Selector" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{D72E3976-2F04-499A-B245-2902252C49BB}" name="Webpage" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4501,502 +5094,730 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="52.140625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="47.140625" style="41" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="1" max="1" width="25.85546875" style="30" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="24" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="24" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="24" customWidth="1"/>
+    <col min="8" max="8" width="42" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:8" ht="15">
+      <c r="A1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="F1" s="51" t="s">
+        <v>650</v>
+      </c>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" spans="1:8" ht="15">
+      <c r="A2" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="34" t="s">
+      <c r="F2" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15">
+      <c r="A3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="34" t="s">
+      <c r="F3" s="52" t="s">
+        <v>578</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30">
+      <c r="A4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="34" t="s">
+      <c r="F4" s="52" t="s">
+        <v>624</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30">
+      <c r="A5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="34" t="s">
+      <c r="F5" s="52" t="s">
+        <v>627</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30">
+      <c r="A6" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="34" t="s">
+      <c r="F6" s="52" t="s">
+        <v>651</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>630</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15">
+      <c r="A7" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="34" t="s">
+      <c r="F7" s="52" t="s">
+        <v>632</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30">
+      <c r="A8" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="34" t="s">
+      <c r="F8" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15">
+      <c r="A9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="34" t="s">
+      <c r="F9" s="52" t="s">
+        <v>638</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30">
+      <c r="A10" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="34" t="s">
+      <c r="F10" s="52" t="s">
+        <v>641</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>642</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="34" t="s">
+      <c r="F11" s="52" t="s">
+        <v>644</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15">
+      <c r="A12" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="34" t="s">
+      <c r="F12" s="52" t="s">
+        <v>647</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="34" t="s">
+    <row r="14" spans="1:8" ht="15">
+      <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="34" t="s">
+      <c r="F14" s="53" t="s">
+        <v>682</v>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+    </row>
+    <row r="15" spans="1:8" ht="15">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="34" t="s">
+      <c r="F15" s="37" t="s">
+        <v>652</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30">
+      <c r="A16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="34" t="s">
+      <c r="F16" s="52" t="s">
+        <v>653</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30">
+      <c r="A17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="34" t="s">
+      <c r="F17" s="52" t="s">
+        <v>656</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>657</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15">
+      <c r="A18" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="34" t="s">
+      <c r="F18" s="52" t="s">
+        <v>659</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>660</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30">
+      <c r="A19" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="34" t="s">
+      <c r="F19" s="52" t="s">
+        <v>662</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="25.5">
+      <c r="A20" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="34" t="s">
+      <c r="F20" s="52" t="s">
+        <v>686</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30">
+      <c r="A21" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="38" t="s">
+      <c r="F21" s="52" t="s">
+        <v>685</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30">
+      <c r="A22" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="40" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="F22" s="52" t="s">
+        <v>683</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30">
+      <c r="A23" s="44" t="s">
         <v>580</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="45" t="s">
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="F23" s="52" t="s">
+        <v>684</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15">
+      <c r="F24" s="52" t="s">
+        <v>673</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15">
+      <c r="F25" s="52" t="s">
+        <v>676</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15">
+      <c r="F26" s="52" t="s">
+        <v>679</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="34" t="s">
         <v>571</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="35" t="s">
         <v>581</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="35" t="s">
         <v>582</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="36" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="24">
-      <c r="A29" s="34" t="s">
+    <row r="29" spans="1:8" ht="24">
+      <c r="A29" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="25" t="s">
         <v>583</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="25" t="s">
         <v>584</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="31" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="34" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="25" t="s">
         <v>586</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="31" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="24">
-      <c r="A31" s="34" t="s">
+    <row r="31" spans="1:8" ht="24">
+      <c r="A31" s="26" t="s">
         <v>577</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="25" t="s">
         <v>587</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="25" t="s">
         <v>588</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="31" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="34" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="26" t="s">
         <v>578</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="25" t="s">
         <v>590</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="25" t="s">
         <v>591</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="31" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="36">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="33" t="s">
         <v>593</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C33" s="33" t="s">
         <v>594</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="31" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-    </row>
-    <row r="37" spans="1:5" s="49" customFormat="1" ht="15">
-      <c r="A37" s="48" t="s">
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+    </row>
+    <row r="37" spans="1:5" ht="15">
+      <c r="A37" s="37" t="s">
         <v>596</v>
       </c>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="37" t="s">
         <v>597</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="37" t="s">
         <v>598</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="37" t="s">
         <v>599</v>
       </c>
-      <c r="E37" s="48" t="s">
+      <c r="E37" s="37" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="22" t="s">
         <v>601</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="23" t="s">
         <v>603</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="23" t="s">
         <v>604</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="23" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="22" t="s">
         <v>606</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="23" t="s">
         <v>608</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="23" t="s">
         <v>609</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="23" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="22" t="s">
         <v>611</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="21" t="s">
         <v>607</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="21" t="s">
         <v>612</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="23" t="s">
         <v>613</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="23" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="45">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="22" t="s">
         <v>615</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="23" t="s">
         <v>617</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="23" t="s">
         <v>618</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="23" t="s">
         <v>619</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F14:H14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" display="https://www.hyrtutorials.com/p/basic-controls.html" xr:uid="{D4D15F97-27E9-44B5-B957-1DC96A1885DD}"/>
@@ -5424,11 +6245,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="12" t="s">
@@ -5541,11 +6362,11 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="12" t="s">
@@ -5708,13 +6529,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
       <c r="P2" s="9" t="s">
         <v>533</v>
       </c>
@@ -6022,10 +6843,10 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="48"/>
       <c r="G14" s="8" t="s">
         <v>190</v>
       </c>
@@ -6108,18 +6929,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="45" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="J1" s="21" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="J1" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="12" t="s">
@@ -6705,12 +7526,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="48" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
@@ -6857,12 +7678,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
@@ -6993,35 +7814,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
       <c r="H1" s="9" t="s">
         <v>427</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="50" t="s">
         <v>514</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="U1" s="26" t="s">
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="U1" s="50" t="s">
         <v>523</v>
       </c>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" s="9" t="s">
@@ -7212,14 +8033,14 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="45" t="s">
         <v>462</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
       <c r="H9" s="11">
         <v>201</v>
       </c>
@@ -7457,15 +8278,15 @@
       <c r="C18" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="H18" s="25" t="s">
+      <c r="H18" s="49" t="s">
         <v>478</v>
       </c>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
       <c r="O18" s="11">
         <v>415</v>
       </c>
